--- a/input/mapping/068. OCB_GOLD_TCKH_GL_ACCT_DIM_BAOANH.xlsx
+++ b/input/mapping/068. OCB_GOLD_TCKH_GL_ACCT_DIM_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1708" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2179FAC1-557F-4D4B-A938-F8EE2B541A29}"/>
+  <xr:revisionPtr revIDLastSave="1715" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECD72A59-AF2D-4CE3-9D08-AB6853234BE1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,12 +113,6 @@
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS GL_ACCT_DIM (
-    DSC         STRING,
-    GL_NBR      INT,
-    LINE_NBR    INT
-)
-USING DELTA;
 TRUNCATE TABLE GL_ACCT_DIM;
 INSERT INTO GL_ACCT_DIM (
     DSC, GL_NBR, LINE_NBR
@@ -2506,7 +2500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3193,9 +3187,6 @@
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" indent="1"/>
@@ -3715,48 +3706,48 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" s="118"/>
-      <c r="B12" s="246" t="s">
+      <c r="B12" s="245" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="247"/>
-      <c r="D12" s="247"/>
-      <c r="E12" s="247"/>
+      <c r="C12" s="246"/>
+      <c r="D12" s="246"/>
+      <c r="E12" s="246"/>
     </row>
     <row r="13" spans="1:48">
       <c r="A13" s="119"/>
-      <c r="B13" s="246" t="s">
+      <c r="B13" s="245" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="247"/>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
+      <c r="C13" s="246"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" s="120"/>
-      <c r="B14" s="246" t="s">
+      <c r="B14" s="245" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="247"/>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" s="121"/>
-      <c r="B15" s="246" t="s">
+      <c r="B15" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="247"/>
-      <c r="D15" s="247"/>
-      <c r="E15" s="247"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" s="122"/>
-      <c r="B16" s="246" t="s">
+      <c r="B16" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="247"/>
-      <c r="D16" s="247"/>
-      <c r="E16" s="247"/>
+      <c r="C16" s="246"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="123" t="s">
@@ -7481,7 +7472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7489,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="138"/>
-      <c r="D3" s="245" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7523,7 +7514,7 @@
       <c r="E1" s="180"/>
       <c r="F1" s="180"/>
       <c r="G1" s="181"/>
-      <c r="H1" s="248"/>
+      <c r="H1" s="247"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="93" t="s">
@@ -7543,7 +7534,7 @@
       </c>
       <c r="F2" s="180"/>
       <c r="G2" s="182"/>
-      <c r="H2" s="248"/>
+      <c r="H2" s="247"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="90">
@@ -7561,7 +7552,7 @@
       <c r="E3" s="183"/>
       <c r="F3" s="183"/>
       <c r="G3" s="184"/>
-      <c r="H3" s="248"/>
+      <c r="H3" s="247"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="90">
@@ -7581,7 +7572,7 @@
       </c>
       <c r="F4" s="183"/>
       <c r="G4" s="184"/>
-      <c r="H4" s="248"/>
+      <c r="H4" s="247"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
       <c r="A5" s="185" t="s">
@@ -7593,7 +7584,7 @@
       <c r="E5" s="186"/>
       <c r="F5" s="186"/>
       <c r="G5" s="187"/>
-      <c r="H5" s="248"/>
+      <c r="H5" s="247"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="93" t="s">
@@ -7617,7 +7608,7 @@
       <c r="G6" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="248"/>
+      <c r="H6" s="247"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="90">
@@ -7641,7 +7632,7 @@
       <c r="G7" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="248"/>
+      <c r="H7" s="247"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="90">
@@ -7665,7 +7656,7 @@
       <c r="G8" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="248"/>
+      <c r="H8" s="247"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="90">
@@ -7689,7 +7680,7 @@
       <c r="G9" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="248"/>
+      <c r="H9" s="247"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="90">
@@ -7713,7 +7704,7 @@
       <c r="G10" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="248"/>
+      <c r="H10" s="247"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="90">
@@ -7737,7 +7728,7 @@
       <c r="G11" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="248"/>
+      <c r="H11" s="247"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="90">
@@ -7761,7 +7752,7 @@
       <c r="G12" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="248"/>
+      <c r="H12" s="247"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="90">
@@ -7785,7 +7776,7 @@
       <c r="G13" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="248"/>
+      <c r="H13" s="247"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="90">
@@ -7809,7 +7800,7 @@
       <c r="G14" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="248"/>
+      <c r="H14" s="247"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="90">
@@ -7833,7 +7824,7 @@
       <c r="G15" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="248"/>
+      <c r="H15" s="247"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="90">
@@ -7857,7 +7848,7 @@
       <c r="G16" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="248"/>
+      <c r="H16" s="247"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="90">
@@ -7881,7 +7872,7 @@
       <c r="G17" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="248"/>
+      <c r="H17" s="247"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="90">
@@ -7905,7 +7896,7 @@
       <c r="G18" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="248"/>
+      <c r="H18" s="247"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="90">
@@ -7929,7 +7920,7 @@
       <c r="G19" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="248"/>
+      <c r="H19" s="247"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="90">
@@ -7953,7 +7944,7 @@
       <c r="G20" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="248"/>
+      <c r="H20" s="247"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="90">
@@ -7977,7 +7968,7 @@
       <c r="G21" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="248"/>
+      <c r="H21" s="247"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="90">
@@ -8001,7 +7992,7 @@
       <c r="G22" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="248"/>
+      <c r="H22" s="247"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="90">
@@ -8025,7 +8016,7 @@
       <c r="G23" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="248"/>
+      <c r="H23" s="247"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="90">
@@ -8049,7 +8040,7 @@
       <c r="G24" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="248"/>
+      <c r="H24" s="247"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="90">
@@ -8073,7 +8064,7 @@
       <c r="G25" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="248"/>
+      <c r="H25" s="247"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="90">
@@ -8097,7 +8088,7 @@
       <c r="G26" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H26" s="248"/>
+      <c r="H26" s="247"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="90">
@@ -8121,7 +8112,7 @@
       <c r="G27" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="248"/>
+      <c r="H27" s="247"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="90">
@@ -8145,7 +8136,7 @@
       <c r="G28" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="248"/>
+      <c r="H28" s="247"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="90">
@@ -8169,7 +8160,7 @@
       <c r="G29" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H29" s="248"/>
+      <c r="H29" s="247"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="90">
@@ -8193,7 +8184,7 @@
       <c r="G30" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H30" s="248"/>
+      <c r="H30" s="247"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="90">
@@ -8217,7 +8208,7 @@
       <c r="G31" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H31" s="248"/>
+      <c r="H31" s="247"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="90">
@@ -8241,7 +8232,7 @@
       <c r="G32" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H32" s="248"/>
+      <c r="H32" s="247"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="90">
@@ -8265,7 +8256,7 @@
       <c r="G33" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="248"/>
+      <c r="H33" s="247"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="90">
@@ -8289,7 +8280,7 @@
       <c r="G34" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="248"/>
+      <c r="H34" s="247"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="90">
@@ -8313,7 +8304,7 @@
       <c r="G35" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="248"/>
+      <c r="H35" s="247"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="90">
@@ -8337,7 +8328,7 @@
       <c r="G36" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="248"/>
+      <c r="H36" s="247"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="90">
@@ -8361,7 +8352,7 @@
       <c r="G37" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H37" s="248"/>
+      <c r="H37" s="247"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="90">
@@ -8385,7 +8376,7 @@
       <c r="G38" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H38" s="248"/>
+      <c r="H38" s="247"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="90">
@@ -8409,7 +8400,7 @@
       <c r="G39" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H39" s="248"/>
+      <c r="H39" s="247"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="90">
@@ -8433,7 +8424,7 @@
       <c r="G40" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="248"/>
+      <c r="H40" s="247"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="90">
@@ -8457,7 +8448,7 @@
       <c r="G41" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H41" s="248"/>
+      <c r="H41" s="247"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="90">
@@ -8481,7 +8472,7 @@
       <c r="G42" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H42" s="248"/>
+      <c r="H42" s="247"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="90">
@@ -8505,7 +8496,7 @@
       <c r="G43" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="248"/>
+      <c r="H43" s="247"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90">
@@ -8529,7 +8520,7 @@
       <c r="G44" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="248"/>
+      <c r="H44" s="247"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90">
@@ -8553,7 +8544,7 @@
       <c r="G45" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="248"/>
+      <c r="H45" s="247"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="90">
@@ -8577,7 +8568,7 @@
       <c r="G46" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H46" s="248"/>
+      <c r="H46" s="247"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="90">
@@ -8601,7 +8592,7 @@
       <c r="G47" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H47" s="248"/>
+      <c r="H47" s="247"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="90">
@@ -8625,7 +8616,7 @@
       <c r="G48" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H48" s="248"/>
+      <c r="H48" s="247"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="90">
@@ -8649,7 +8640,7 @@
       <c r="G49" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H49" s="248"/>
+      <c r="H49" s="247"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="90">
@@ -8673,7 +8664,7 @@
       <c r="G50" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H50" s="248"/>
+      <c r="H50" s="247"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="90">
@@ -8697,7 +8688,7 @@
       <c r="G51" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H51" s="248"/>
+      <c r="H51" s="247"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="90">
@@ -8721,7 +8712,7 @@
       <c r="G52" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H52" s="248"/>
+      <c r="H52" s="247"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="90">
@@ -8745,7 +8736,7 @@
       <c r="G53" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H53" s="248"/>
+      <c r="H53" s="247"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="90">
@@ -8769,7 +8760,7 @@
       <c r="G54" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H54" s="248"/>
+      <c r="H54" s="247"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="90">
@@ -8793,7 +8784,7 @@
       <c r="G55" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H55" s="248"/>
+      <c r="H55" s="247"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="90">
@@ -8817,7 +8808,7 @@
       <c r="G56" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H56" s="248"/>
+      <c r="H56" s="247"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="90">
@@ -8841,7 +8832,7 @@
       <c r="G57" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="H57" s="248"/>
+      <c r="H57" s="247"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="114">
@@ -8865,137 +8856,137 @@
       <c r="G58" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="H58" s="248"/>
+      <c r="H58" s="247"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="249">
+      <c r="A59" s="248">
         <v>53</v>
       </c>
-      <c r="B59" s="250" t="s">
+      <c r="B59" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="251" t="s">
+      <c r="C59" s="250" t="s">
         <v>152</v>
       </c>
-      <c r="D59" s="252" t="s">
+      <c r="D59" s="251" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="253" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="250" t="s">
+      <c r="E59" s="252" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="249" t="s">
         <v>153</v>
       </c>
-      <c r="G59" s="250" t="s">
+      <c r="G59" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="H59" s="248"/>
+      <c r="H59" s="247"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="249">
+      <c r="A60" s="248">
         <v>54</v>
       </c>
-      <c r="B60" s="250" t="s">
+      <c r="B60" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="251" t="s">
+      <c r="C60" s="250" t="s">
         <v>154</v>
       </c>
-      <c r="D60" s="252" t="s">
+      <c r="D60" s="251" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="253" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="250" t="s">
+      <c r="E60" s="252" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="249" t="s">
         <v>155</v>
       </c>
-      <c r="G60" s="250" t="s">
+      <c r="G60" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="H60" s="248"/>
+      <c r="H60" s="247"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="249">
+      <c r="A61" s="248">
         <v>55</v>
       </c>
-      <c r="B61" s="250" t="s">
+      <c r="B61" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="251" t="s">
+      <c r="C61" s="250" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="252" t="s">
+      <c r="D61" s="251" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="253" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="250" t="s">
+      <c r="E61" s="252" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="249" t="s">
         <v>157</v>
       </c>
-      <c r="G61" s="250" t="s">
+      <c r="G61" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="H61" s="248"/>
+      <c r="H61" s="247"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="249">
+      <c r="A62" s="248">
         <v>56</v>
       </c>
-      <c r="B62" s="250" t="s">
+      <c r="B62" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="251" t="s">
+      <c r="C62" s="250" t="s">
         <v>158</v>
       </c>
-      <c r="D62" s="252" t="s">
+      <c r="D62" s="251" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="253" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="250" t="s">
+      <c r="E62" s="252" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="249" t="s">
         <v>159</v>
       </c>
-      <c r="G62" s="250" t="s">
+      <c r="G62" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="H62" s="248"/>
+      <c r="H62" s="247"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="249">
+      <c r="A63" s="248">
         <v>57</v>
       </c>
-      <c r="B63" s="250" t="s">
+      <c r="B63" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="251" t="s">
+      <c r="C63" s="250" t="s">
         <v>160</v>
       </c>
-      <c r="D63" s="252" t="s">
+      <c r="D63" s="251" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="253" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="250" t="s">
+      <c r="E63" s="252" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="249" t="s">
         <v>161</v>
       </c>
-      <c r="G63" s="250" t="s">
+      <c r="G63" s="249" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="248"/>
+      <c r="H63" s="247"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="254"/>
-      <c r="B64" s="248"/>
-      <c r="C64" s="254"/>
-      <c r="D64" s="254"/>
-      <c r="E64" s="248"/>
-      <c r="F64" s="248"/>
-      <c r="G64" s="248"/>
-      <c r="H64" s="255"/>
+      <c r="A64" s="253"/>
+      <c r="B64" s="247"/>
+      <c r="C64" s="253"/>
+      <c r="D64" s="253"/>
+      <c r="E64" s="247"/>
+      <c r="F64" s="247"/>
+      <c r="G64" s="247"/>
+      <c r="H64" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9289,12 +9280,12 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="255"/>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
+      <c r="A5" s="254"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="196" t="s">
@@ -9304,7 +9295,7 @@
       <c r="C7" s="202"/>
       <c r="D7" s="202"/>
       <c r="E7" s="202"/>
-      <c r="F7" s="255"/>
+      <c r="F7" s="254"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="46" t="s">
@@ -9322,7 +9313,7 @@
       <c r="E8" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="F8" s="255"/>
+      <c r="F8" s="254"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="51" t="s">
@@ -9340,7 +9331,7 @@
       <c r="E9" s="54" t="s">
         <v>193</v>
       </c>
-      <c r="F9" s="255"/>
+      <c r="F9" s="254"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="51" t="s">
@@ -9358,7 +9349,7 @@
       <c r="E10" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="F10" s="255"/>
+      <c r="F10" s="254"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="51" t="s">
@@ -9376,7 +9367,7 @@
       <c r="E11" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="F11" s="255"/>
+      <c r="F11" s="254"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="51" t="s">
@@ -9394,7 +9385,7 @@
       <c r="E12" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="255"/>
+      <c r="F12" s="254"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="51" t="s">
@@ -9412,7 +9403,7 @@
       <c r="E13" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="255"/>
+      <c r="F13" s="254"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="51" t="s">
@@ -9430,7 +9421,7 @@
       <c r="E14" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="255"/>
+      <c r="F14" s="254"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="51" t="s">
@@ -9448,7 +9439,7 @@
       <c r="E15" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="255"/>
+      <c r="F15" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12280,25 +12271,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -12470,8 +12442,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12479,5 +12470,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>